--- a/data/trans_bre/P16A03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A03-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,46</t>
+          <t>2,05; 5,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 8,16</t>
+          <t>4,64; 8,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,66</t>
+          <t>2,22; 5,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,02</t>
+          <t>1,51; 6,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,61; 249,97</t>
+          <t>47,35; 254,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>163,88; 772,91</t>
+          <t>183,29; 879,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,73; 541,02</t>
+          <t>83,43; 546,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,78; 187,75</t>
+          <t>23,13; 194,97</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,49</t>
+          <t>1,97; 4,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,49</t>
+          <t>2,19; 4,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,22</t>
+          <t>1,21; 3,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,41</t>
+          <t>1,16; 3,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>100,52; 453,89</t>
+          <t>98,12; 411,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>138,26; 563,2</t>
+          <t>139,49; 550,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,42; 382,32</t>
+          <t>80,44; 366,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,42; 288,12</t>
+          <t>66,84; 295,92</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 2,68</t>
+          <t>-2,4; 2,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,1</t>
+          <t>1,79; 6,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,7</t>
+          <t>1,65; 5,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,75</t>
+          <t>0,85; 4,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,52; 119,2</t>
+          <t>-52,02; 108,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,9; 1109,48</t>
+          <t>42,52; 1031,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,44; 1099,18</t>
+          <t>70,37; 1115,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,81; 446,27</t>
+          <t>23,24; 450,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,99</t>
+          <t>2,15; 4,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,58</t>
+          <t>3,81; 5,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,7</t>
+          <t>2,11; 3,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,84</t>
+          <t>1,84; 3,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,59; 222,67</t>
+          <t>79,37; 217,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>229,38; 543,62</t>
+          <t>220,98; 520,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>135,21; 377,52</t>
+          <t>128,32; 363,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>82,41; 237,83</t>
+          <t>82,32; 237,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A03-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A03-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>102,92%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,66</t>
+          <t>2,08; 5,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,27</t>
+          <t>4,67; 8,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,63</t>
+          <t>2,19; 5,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,06</t>
+          <t>1,95; 6,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,35; 254,92</t>
+          <t>52,88; 259,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>183,29; 879,85</t>
+          <t>173,39; 850,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,43; 546,2</t>
+          <t>87,19; 532,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,13; 194,97</t>
+          <t>33,89; 203,34</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>154,28%</t>
+          <t>140,46%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,43</t>
+          <t>2,04; 4,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,41</t>
+          <t>2,32; 4,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,12</t>
+          <t>1,35; 3,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,41</t>
+          <t>1,61; 3,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>98,12; 411,95</t>
+          <t>100,87; 391,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>139,49; 550,67</t>
+          <t>148,39; 618,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,44; 366,16</t>
+          <t>83,04; 395,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,84; 295,92</t>
+          <t>66,23; 243,16</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>3,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>156,23%</t>
+          <t>186,51%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,47</t>
+          <t>-2,1; 2,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,87</t>
+          <t>1,67; 6,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,87</t>
+          <t>1,65; 5,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,89</t>
+          <t>1,54; 4,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,02; 108,05</t>
+          <t>-49,66; 117,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,52; 1031,8</t>
+          <t>40,26; 947,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,37; 1115,79</t>
+          <t>60,1; 1079,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,24; 450,29</t>
+          <t>49,35; 524,28</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>146,72%</t>
+          <t>145,67%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,06</t>
+          <t>2,09; 4,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,56</t>
+          <t>3,61; 5,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,73</t>
+          <t>2,18; 3,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,83</t>
+          <t>2,32; 3,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,37; 217,92</t>
+          <t>78,61; 215,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>220,98; 520,43</t>
+          <t>215,6; 526,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>128,32; 363,66</t>
+          <t>133,1; 362,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>82,32; 237,89</t>
+          <t>88,22; 209,33</t>
         </is>
       </c>
     </row>
